--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1864,7 +1864,7 @@
         <v>45839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1937,7 +1937,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2010,7 +2010,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2156,7 +2156,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2229,7 +2229,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2302,7 +2302,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9.4</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2375,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2448,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2521,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2594,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2740,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2813,7 +2813,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2886,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2942,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +2959,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3032,7 +3032,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3105,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3161,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3178,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3234,7 +3234,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3251,7 +3251,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3307,7 +3307,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,7 +3324,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3380,7 +3380,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3397,7 +3397,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3463,14 +3463,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45826</v>
+        <v>44935</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3482,8 +3482,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3526,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3536,14 +3541,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45251</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3599,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3609,14 +3614,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3628,13 +3633,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3694,7 +3694,7 @@
         <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3767,7 +3767,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,8 +3852,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45201</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3936,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +3989,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4061,10 +4066,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4082,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4243,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,8 +1556,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1566,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1584,55 +1589,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1642,14 +1647,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1661,13 +1666,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,8 +1876,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1930,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2010,7 +2015,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2076,14 +2081,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2101,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2149,14 +2154,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2174,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2217,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2222,14 +2227,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2241,8 +2246,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2295,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2295,14 +2305,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2314,8 +2324,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2373,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2368,14 +2383,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2387,8 +2402,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2451,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2441,14 +2461,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2460,8 +2480,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2529,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2518,10 +2543,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2559,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2602,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2587,14 +2612,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2606,8 +2631,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2680,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2697,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2710,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.5</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2753,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2770,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2783,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2826,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2813,7 +2843,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2856,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2899,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2916,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2929,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2972,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +2989,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +3002,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3015,7 +3045,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3032,7 +3062,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3088,7 +3118,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3135,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3148,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3191,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3208,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3221,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3234,7 +3264,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3251,7 +3281,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3264,7 +3294,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3307,7 +3337,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,7 +3354,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3337,7 +3367,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3380,7 +3410,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3397,7 +3427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3410,7 +3440,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>9.4</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3453,7 +3483,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3463,14 +3493,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3482,13 +3512,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3556,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3570,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3586,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3629,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3621,7 +3646,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3659,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3702,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,14 +3712,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3750,7 +3775,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,14 +3785,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3805,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3848,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3858,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,13 +3877,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3921,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3911,14 +3931,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,13 +3950,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>10.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3994,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3989,14 +4004,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4009,7 +4024,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4067,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4062,14 +4077,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,13 +4096,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4140,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4140,14 +4150,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4159,13 +4169,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4213,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4218,14 +4223,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4237,13 +4242,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,13 +1556,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1571,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1589,55 +1584,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,14 +1642,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1666,8 +1661,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44930</v>
+        <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2081,14 +2081,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2154,14 +2154,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2217,7 +2217,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2227,14 +2227,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2246,13 +2246,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2295,7 +2290,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2305,14 +2300,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2324,13 +2319,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2373,7 +2363,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2383,14 +2373,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2402,13 +2392,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2451,7 +2436,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2461,14 +2446,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2480,13 +2465,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2529,7 +2509,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2543,10 +2523,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2559,7 +2539,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2602,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2612,14 +2592,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2631,13 +2611,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2680,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2697,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2710,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2753,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2770,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2783,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2826,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2843,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2899,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2916,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2929,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2972,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2989,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3002,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3045,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3062,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3075,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3118,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3135,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3148,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.4</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3191,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3208,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3221,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3264,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3281,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3294,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3337,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3354,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3367,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3410,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3427,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3440,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3483,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3500,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3513,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3556,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3570,10 +3545,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3586,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3629,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3639,14 +3614,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3659,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3702,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3712,14 +3687,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3732,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3775,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3792,7 +3767,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3805,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3848,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3858,14 +3833,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3877,8 +3852,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3921,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3931,14 +3911,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3950,8 +3930,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3994,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4004,14 +3989,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4024,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4067,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4077,14 +4062,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4096,8 +4081,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4140,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4150,14 +4140,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4169,8 +4159,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4213,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4223,14 +4218,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4242,8 +4237,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45826</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,13 +1876,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,7 +1937,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,7 +2010,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2088,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,7 +2156,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2229,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2290,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2307,7 +2302,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2320,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2363,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2380,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2393,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2436,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2453,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2466,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2509,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2526,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2599,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2672,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2745,7 +2740,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2758,7 +2753,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2813,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2886,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2899,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2942,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2959,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2972,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3015,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3032,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3045,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3088,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3105,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3118,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3161,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3178,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3191,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3234,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3251,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3264,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3307,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3324,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3385,7 +3380,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3397,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3410,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3453,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3483,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3526,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,14 +3536,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3556,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3599,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,14 +3609,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3629,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3672,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3691,10 +3686,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>44915</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3706,8 +3701,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,14 +3760,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,8 +3779,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3828,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3838,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45201</v>
+        <v>45222</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,13 +3857,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,13 +3930,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3993,10 +3988,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4009,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4066,10 +4061,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4087,7 +4082,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4139,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4243,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,8 +1556,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1566,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1584,55 +1589,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1642,14 +1647,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1661,13 +1666,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,8 +1876,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1930,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2003,14 +2008,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2076,14 +2081,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2095,8 +2100,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2149,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2149,14 +2159,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2168,8 +2178,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2227,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2222,14 +2237,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2257,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2300,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2295,14 +2310,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2314,8 +2329,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2378,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2368,14 +2388,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2387,8 +2407,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2456,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2448,7 +2473,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2486,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2529,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2514,14 +2539,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2533,8 +2558,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2607,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2591,10 +2621,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2637,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2680,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2697,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2710,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2753,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2770,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2783,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2826,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2813,7 +2843,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2856,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2899,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2916,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2929,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2972,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +2989,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +3002,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3015,7 +3045,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3032,7 +3062,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3045,7 +3075,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3088,7 +3118,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3135,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3148,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3191,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3208,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3221,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3234,7 +3264,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3251,7 +3281,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3264,7 +3294,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3307,7 +3337,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,7 +3354,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3337,7 +3367,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3380,7 +3410,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3397,7 +3427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3410,7 +3440,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3453,7 +3483,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3467,10 +3497,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3483,7 +3513,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3526,7 +3556,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3536,14 +3566,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,7 +3586,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3599,7 +3629,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3616,7 +3646,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3629,7 +3659,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3672,7 +3702,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3682,14 +3712,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3701,13 +3731,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3775,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,14 +3785,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,13 +3804,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3828,7 +3848,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3842,10 +3862,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3858,7 +3878,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3921,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3911,14 +3931,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3951,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3994,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +4004,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4024,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4067,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4057,14 +4077,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,13 +4096,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4140,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4135,14 +4150,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,13 +4169,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4213,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4213,14 +4223,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4232,13 +4242,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45201</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>44915</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45201</v>
+        <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2100,13 +2100,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2149,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44930</v>
+        <v>45201</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2184,7 +2179,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2227,7 +2222,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2241,10 +2236,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45251</v>
+        <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2256,8 +2251,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2300,7 +2300,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44915</v>
+        <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2329,13 +2329,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2378,7 +2373,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45078</v>
+        <v>44915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2413,7 +2408,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2456,7 +2451,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2466,14 +2461,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2485,8 +2480,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2843,7 +2843,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4157,7 +4157,7 @@
         <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,13 +1556,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1571,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1589,55 +1584,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,14 +1642,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1666,8 +1661,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44935</v>
+        <v>44915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,8 +1954,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +2003,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2012,10 +2017,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45995</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2033,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2076,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2081,14 +2086,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45995</v>
+        <v>45222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2101,7 +2106,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2149,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45201</v>
+        <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2173,13 +2178,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2251,13 +2251,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2300,7 +2295,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2310,14 +2305,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2330,7 +2325,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2373,7 +2368,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2383,14 +2378,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2402,13 +2397,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2451,7 +2441,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2461,14 +2451,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2480,13 +2470,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2529,7 +2514,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2539,14 +2524,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2558,13 +2543,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2607,7 +2587,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2621,10 +2601,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2637,7 +2617,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2680,7 +2660,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2697,7 +2677,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2710,7 +2690,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2753,7 +2733,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2770,7 +2750,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2783,7 +2763,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2826,7 +2806,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2843,7 +2823,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2856,7 +2836,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2899,7 +2879,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2916,7 +2896,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2929,7 +2909,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2972,7 +2952,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2989,7 +2969,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3002,7 +2982,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3045,7 +3025,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3062,7 +3042,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3075,7 +3055,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3118,7 +3098,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3135,7 +3115,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3148,7 +3128,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3191,7 +3171,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3208,7 +3188,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3221,7 +3201,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3264,7 +3244,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3281,7 +3261,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3294,7 +3274,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3337,7 +3317,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3354,7 +3334,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3367,7 +3347,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3410,7 +3390,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3427,7 +3407,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3440,7 +3420,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3483,7 +3463,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3500,7 +3480,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3513,7 +3493,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3556,7 +3536,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3573,7 +3553,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3586,7 +3566,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3629,7 +3609,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3646,7 +3626,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3659,7 +3639,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3702,7 +3682,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3719,7 +3699,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3732,7 +3712,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3775,7 +3755,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3792,7 +3772,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3805,7 +3785,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3848,7 +3828,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3865,7 +3845,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3878,7 +3858,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3921,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3931,14 +3911,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3950,8 +3930,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3994,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4008,10 +3993,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4024,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4067,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4077,14 +4062,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4096,8 +4081,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4140,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4150,14 +4140,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4169,8 +4159,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4213,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4223,14 +4218,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4242,8 +4237,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,8 +1556,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1566,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1584,55 +1589,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1642,14 +1647,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1661,13 +1666,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44915</v>
+        <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,13 +1954,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2003,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,10 +2012,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2033,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2076,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2086,14 +2081,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45222</v>
+        <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2106,7 +2101,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2149,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2163,10 +2158,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45995</v>
+        <v>45201</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2178,8 +2173,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>44930</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2251,8 +2251,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2295,7 +2300,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2305,14 +2310,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2325,7 +2330,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2368,7 +2373,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2378,14 +2383,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2397,8 +2402,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2441,7 +2451,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2451,14 +2461,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2470,8 +2480,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2514,7 +2529,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2524,14 +2539,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2543,8 +2558,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2587,7 +2607,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2601,10 +2621,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2617,7 +2637,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2660,7 +2680,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2677,7 +2697,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2690,7 +2710,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2733,7 +2753,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2750,7 +2770,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2763,7 +2783,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2806,7 +2826,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2823,7 +2843,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2836,7 +2856,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2879,7 +2899,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2896,7 +2916,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2909,7 +2929,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2952,7 +2972,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2969,7 +2989,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2982,7 +3002,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3025,7 +3045,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3042,7 +3062,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3055,7 +3075,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3098,7 +3118,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3115,7 +3135,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3128,7 +3148,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3171,7 +3191,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3188,7 +3208,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3201,7 +3221,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3244,7 +3264,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3261,7 +3281,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3274,7 +3294,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3317,7 +3337,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3334,7 +3354,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3347,7 +3367,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3390,7 +3410,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3407,7 +3427,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3420,7 +3440,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3463,7 +3483,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3480,7 +3500,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3493,7 +3513,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3536,7 +3556,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3553,7 +3573,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3566,7 +3586,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3609,7 +3629,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3626,7 +3646,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3639,7 +3659,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3682,7 +3702,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3699,7 +3719,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3712,7 +3732,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3755,7 +3775,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3772,7 +3792,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3785,7 +3805,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3828,7 +3848,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3845,7 +3865,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3858,7 +3878,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3921,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3911,14 +3931,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,13 +3950,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3994,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3993,10 +4008,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4009,7 +4024,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4067,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4062,14 +4077,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,13 +4096,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4140,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4140,14 +4150,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4159,13 +4169,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4213,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4218,14 +4223,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4237,13 +4242,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,13 +1556,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1571,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1589,55 +1584,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,14 +1642,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1666,8 +1661,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44935</v>
+        <v>45251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,13 +1876,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1930,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2015,7 +2010,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2071,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2081,14 +2076,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2101,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2158,10 +2153,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45201</v>
+        <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2179,7 +2174,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2222,7 +2217,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2232,14 +2227,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2251,13 +2246,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2300,7 +2290,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2310,14 +2300,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2330,7 +2320,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2373,7 +2363,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2383,14 +2373,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2402,13 +2392,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2451,7 +2436,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2461,14 +2446,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2480,13 +2465,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2529,7 +2509,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2539,14 +2519,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2558,13 +2538,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2607,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2621,10 +2596,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2637,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2680,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2697,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2710,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>9.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2753,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2770,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2783,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2826,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2843,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2856,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2899,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2916,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2929,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2972,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2989,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3002,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3045,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3062,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3075,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3118,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3135,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3148,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3191,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3208,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3221,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3264,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3281,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3294,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3354,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3427,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3556,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3573,7 +3548,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3586,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3629,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3646,7 +3621,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3702,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3719,7 +3694,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3732,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3775,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3792,7 +3767,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3805,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3848,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3862,10 +3837,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3878,7 +3853,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3921,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3931,14 +3906,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3950,8 +3925,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3994,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4008,10 +3988,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4024,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4067,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4077,14 +4057,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4096,8 +4076,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4140,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4150,14 +4135,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4169,8 +4154,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4213,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4223,14 +4213,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4242,8 +4232,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45826</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>45251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45826</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>45251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45826</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1930,14 +1930,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2003,14 +2003,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2149,14 +2149,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2168,13 +2168,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2217,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2234,7 +2229,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2247,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2290,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2307,7 +2302,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2320,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2363,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2380,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2393,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2436,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2453,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2466,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2509,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2526,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2599,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2672,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2738,14 +2733,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2757,8 +2752,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,14 +3614,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,14 +3687,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3767,7 +3767,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45826</v>
+        <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,8 +3852,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45201</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3936,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +3989,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4061,10 +4066,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4082,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4243,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1864,7 +1864,7 @@
         <v>45839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1937,7 +1937,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2010,7 +2010,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2156,7 +2156,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2229,7 +2229,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2302,7 +2302,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2375,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2448,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2521,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2594,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2733,14 +2733,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2752,13 +2752,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2813,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2886,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2899,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2942,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2959,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2972,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3015,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3032,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3045,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3088,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3105,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3118,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3161,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3178,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3191,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3234,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3251,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3264,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3307,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3324,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3385,7 +3380,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3397,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3410,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3453,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3483,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3526,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,14 +3536,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3556,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3599,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3621,7 +3616,7 @@
         <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3629,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3672,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3694,7 +3689,7 @@
         <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3702,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3745,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,14 +3755,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,8 +3774,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,13 +3852,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3936,7 +3931,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3989,14 +3984,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4009,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4066,10 +4061,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4087,7 +4082,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4139,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4243,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,8 +1556,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1566,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1584,55 +1589,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1642,14 +1647,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1661,13 +1666,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,8 +1876,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1930,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1949,8 +1954,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +2003,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2003,14 +2013,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2033,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2076,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2080,10 +2090,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2106,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2149,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2149,14 +2159,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2168,8 +2178,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2227,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2222,14 +2237,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2241,8 +2256,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2305,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2295,14 +2315,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2314,8 +2334,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>9.4</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2383,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2375,7 +2400,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2413,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2448,7 +2473,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2504,7 +2529,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2521,7 +2546,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2559,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2602,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2594,7 +2619,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2632,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2675,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2692,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2705,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2748,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2765,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2778,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2813,7 +2838,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2869,7 +2894,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2911,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2924,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2967,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +2984,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2997,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3015,7 +3040,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3032,7 +3057,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3045,7 +3070,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3088,7 +3113,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3130,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3143,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3186,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3203,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3216,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3234,7 +3259,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3251,7 +3276,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3264,7 +3289,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3307,7 +3332,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,7 +3349,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3337,7 +3362,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3380,7 +3405,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3397,7 +3422,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3410,7 +3435,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3453,7 +3478,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3467,10 +3492,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3483,7 +3508,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3526,7 +3551,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3536,14 +3561,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,7 +3581,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3599,7 +3624,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3609,14 +3634,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3629,7 +3654,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3672,7 +3697,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3682,14 +3707,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3702,7 +3727,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3745,7 +3770,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3755,14 +3780,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3774,13 +3799,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3843,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3840,7 +3860,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3873,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3916,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,14 +3926,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,13 +3945,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3989,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +3999,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45359</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,8 +4018,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4067,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4057,14 +4077,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>45826</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4076,13 +4096,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4140,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4154,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45995</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4154,13 +4169,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4213,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4227,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4232,13 +4242,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,13 +1556,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1571,10 +1566,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1589,55 +1584,55 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1647,14 +1642,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1666,8 +1661,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,48 +1694,48 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45201</v>
+        <v>45251</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,13 +1876,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,13 +1949,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2003,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,10 +2007,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2033,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2076,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2090,10 +2080,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2106,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2149,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2159,14 +2149,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2178,13 +2168,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2227,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2237,14 +2222,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2256,13 +2241,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2305,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2315,14 +2295,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2334,13 +2314,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2383,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2400,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2413,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2456,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2473,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2486,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2529,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2546,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2559,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2602,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2619,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2632,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>9.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2675,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2692,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2705,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2748,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2765,7 +2740,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2778,7 +2753,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2821,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2838,7 +2813,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2851,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2894,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2911,7 +2886,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2924,7 +2899,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2967,7 +2942,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2984,7 +2959,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2997,7 +2972,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3040,7 +3015,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3057,7 +3032,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3070,7 +3045,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3113,7 +3088,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3130,7 +3105,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3143,7 +3118,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3186,7 +3161,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3203,7 +3178,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3216,7 +3191,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3259,7 +3234,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3276,7 +3251,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3289,7 +3264,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3332,7 +3307,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3349,7 +3324,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3362,7 +3337,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3405,7 +3380,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3422,7 +3397,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3435,7 +3410,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3478,7 +3453,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3495,7 +3470,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3508,7 +3483,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3551,7 +3526,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3568,7 +3543,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3581,7 +3556,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3624,7 +3599,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3641,7 +3616,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3654,7 +3629,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3697,7 +3672,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3714,7 +3689,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3727,7 +3702,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3770,7 +3745,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3784,10 +3759,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3800,7 +3775,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3843,7 +3818,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3853,14 +3828,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3872,8 +3847,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>5.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3916,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3926,14 +3906,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3945,8 +3925,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>9.4</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3989,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3999,14 +3984,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45359</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4018,13 +4003,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4067,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4077,14 +4057,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45826</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4096,8 +4076,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4140,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4154,10 +4139,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45995</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4169,8 +4154,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4213,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4227,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45995</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4242,8 +4232,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45251</v>
+        <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,8 +1876,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1937,7 +1942,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2010,7 +2015,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,7 +2088,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2101,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2156,7 +2161,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2174,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2217,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2229,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2247,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2290,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2302,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2320,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2363,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2375,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2393,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2436,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2448,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2466,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2509,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2521,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2594,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2813,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3032,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3088,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3234,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3251,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3264,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3307,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3337,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3380,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3397,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3410,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3453,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3470,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3483,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3526,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3543,7 +3548,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3599,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3616,7 +3621,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3629,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3672,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3689,7 +3694,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3702,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3762,7 +3767,7 @@
         <v>45826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3818,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3832,10 +3837,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44915</v>
+        <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3858,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45201</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3936,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +3989,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4061,10 +4066,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4082,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4243,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,13 +1876,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1930,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,14 +2003,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2088,7 +2083,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2101,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2161,7 +2156,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2174,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2217,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2234,7 +2229,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2247,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2290,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2307,7 +2302,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2320,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>9.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2363,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2380,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2393,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2436,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2453,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2466,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2509,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2526,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2539,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2599,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2672,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2745,7 +2740,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2758,7 +2753,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2813,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2886,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2899,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2942,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2959,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2972,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3015,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3032,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3045,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3088,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3105,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3118,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3161,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3178,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3191,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3234,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3251,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3264,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3307,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3324,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3337,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3380,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3397,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3410,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3453,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3483,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3526,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3541,14 +3536,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3556,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3599,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,14 +3609,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3629,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9.4</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3672,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,14 +3682,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3702,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3745,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,14 +3755,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45826</v>
+        <v>44915</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3779,8 +3774,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,13 +3852,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3936,7 +3931,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3989,14 +3984,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4009,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4066,10 +4061,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4087,7 +4082,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4139,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4243,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,8 +1876,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1920,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1937,7 +1942,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2010,7 +2015,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2083,7 +2088,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2161,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2285,7 +2290,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2302,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2320,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2363,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2375,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2393,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2436,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2448,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2466,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2509,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2521,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2539,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2594,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2667,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2813,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3015,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3032,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3045,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3088,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3234,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3251,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3264,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3307,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3324,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3380,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3397,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3410,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3453,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3467,10 +3472,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3483,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3526,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3536,14 +3541,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45251</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3599,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3609,14 +3614,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3629,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3689,7 +3694,7 @@
         <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3745,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3759,10 +3764,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44915</v>
+        <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3774,13 +3779,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3833,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,8 +3852,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45201</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3936,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +3989,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4061,10 +4066,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4082,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4243,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44935</v>
+        <v>44915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,7 +1942,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2088,7 +2088,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2161,7 +2161,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2217,7 +2217,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2234,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2307,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2363,7 +2363,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2453,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2526,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2599,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2672,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2745,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,14 +3614,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,8 +3633,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3682,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,14 +3692,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>45222</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3712,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3755,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3760,14 +3765,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3785,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3828,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3837,10 +3842,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45201</v>
+        <v>45251</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,13 +3857,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,13 +3930,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3993,10 +3988,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4009,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4066,10 +4061,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4087,7 +4082,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4139,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4165,7 +4160,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4222,10 +4217,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4243,7 +4238,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44915</v>
+        <v>44935</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1942,7 +1942,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2015,7 +2015,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2088,7 +2088,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2161,7 +2161,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2217,7 +2217,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2234,7 +2234,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2307,7 +2307,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2363,7 +2363,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9.4</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2436,7 +2436,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2453,7 +2453,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2526,7 +2526,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2599,7 +2599,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2672,7 +2672,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2745,7 +2745,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2818,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2891,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2964,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3037,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3110,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3183,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3256,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3329,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3402,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3475,7 +3475,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45201</v>
+        <v>45995</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3633,13 +3633,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3682,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3692,14 +3687,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45222</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3712,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3772,7 +3767,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3828,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3842,10 +3837,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45251</v>
+        <v>45201</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3857,8 +3852,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45995</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,8 +3930,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3979,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3988,10 +3993,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45995</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +4009,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4061,10 +4066,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4082,7 +4087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4130,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4144,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4165,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4203,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4217,10 +4222,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4238,7 +4243,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4281,7 +4286,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4291,14 +4296,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4310,13 +4315,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44935</v>
+        <v>44915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,8 +1954,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1998,7 +2003,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2008,14 +2013,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2027,8 +2032,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2071,7 +2081,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2081,14 +2091,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2100,8 +2110,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2144,7 +2159,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2158,10 +2173,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2174,7 +2189,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2217,7 +2232,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2227,14 +2242,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2247,7 +2262,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2290,7 +2305,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2307,7 +2322,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2320,7 +2335,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2363,7 +2378,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2380,7 +2395,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2393,7 +2408,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2436,7 +2451,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2453,7 +2468,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2466,7 +2481,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2509,7 +2524,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2526,7 +2541,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2539,7 +2554,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2597,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2599,7 +2614,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2627,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2670,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2672,7 +2687,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2700,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2743,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2745,7 +2760,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2758,7 +2773,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2816,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2818,7 +2833,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2846,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2889,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2891,7 +2906,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2904,7 +2919,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2962,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2964,7 +2979,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2992,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3035,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3037,7 +3052,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3065,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3093,7 +3108,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3110,7 +3125,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3123,7 +3138,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3166,7 +3181,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3183,7 +3198,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3239,7 +3254,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3256,7 +3271,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3284,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3327,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3329,7 +3344,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3357,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3400,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3402,7 +3417,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3430,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3473,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3475,7 +3490,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3503,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9.4</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3546,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3560,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3576,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3619,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3614,14 +3629,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3649,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3692,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3687,14 +3702,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3722,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3765,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3767,7 +3782,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3795,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3838,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3833,14 +3848,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3852,13 +3867,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3901,7 +3911,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3911,14 +3921,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3930,13 +3940,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3979,7 +3984,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3993,10 +3998,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4008,8 +4013,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4062,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4066,10 +4076,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>45995</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,13 +4091,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4130,7 +4135,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4144,10 +4149,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45995</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4159,13 +4164,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4208,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4218,14 +4218,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4235,11 +4235,6 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -4286,7 +4281,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4296,14 +4291,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4315,8 +4310,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>44935</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45201</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>45222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45995</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45995</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>44915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>45078</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>44935</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2098,7 +2098,7 @@
         <v>45201</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>45222</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
         <v>45995</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>45995</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45098</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1857,14 +1857,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44915</v>
+        <v>45222</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1876,13 +1876,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1925,7 +1920,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1939,10 +1934,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45078</v>
+        <v>45995</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1954,13 +1949,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2003,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2017,10 +2007,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44935</v>
+        <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2032,13 +2022,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2081,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2091,14 +2076,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2110,13 +2095,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2159,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2173,10 +2153,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2189,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2232,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2242,14 +2222,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2262,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2305,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2322,7 +2302,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2335,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2378,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2395,7 +2375,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2408,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2468,7 +2448,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2524,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2541,7 +2521,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2554,7 +2534,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2597,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2614,7 +2594,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2627,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2670,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2687,7 +2667,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2700,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2743,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2760,7 +2740,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2773,7 +2753,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2816,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2833,7 +2813,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2846,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2889,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2906,7 +2886,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2919,7 +2899,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2962,7 +2942,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2979,7 +2959,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2992,7 +2972,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3035,7 +3015,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3052,7 +3032,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3065,7 +3045,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3125,7 +3105,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3181,7 +3161,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3198,7 +3178,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3211,7 +3191,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3254,7 +3234,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3271,7 +3251,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3284,7 +3264,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3327,7 +3307,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3344,7 +3324,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3357,7 +3337,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3400,7 +3380,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3417,7 +3397,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3430,7 +3410,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3473,7 +3453,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3490,7 +3470,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3503,7 +3483,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3546,7 +3526,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3563,7 +3543,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3576,7 +3556,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3619,7 +3599,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3636,7 +3616,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3649,7 +3629,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>9.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3692,7 +3672,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3706,10 +3686,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3722,7 +3702,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3765,7 +3745,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3782,7 +3762,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3795,7 +3775,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3838,7 +3818,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3848,14 +3828,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3867,8 +3847,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3911,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3921,14 +3906,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45826</v>
+        <v>45201</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3940,8 +3925,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4001,7 +3991,7 @@
         <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4062,7 +4052,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4076,10 +4066,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45995</v>
+        <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4092,7 +4082,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4135,7 +4125,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4149,10 +4139,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45995</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4164,8 +4154,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4208,7 +4203,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4218,14 +4213,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4237,8 +4232,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
         <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1556,20 +1556,25 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1584,55 +1589,60 @@
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Talltita
+Tofsmes</t>
         </is>
       </c>
       <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
         <v/>
       </c>
       <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
         <v/>
       </c>
       <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
         <v/>
       </c>
       <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
         <v/>
       </c>
       <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
       <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1642,14 +1652,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1661,13 +1671,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1676,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1694,72 +1699,72 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S 2180-2023</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45098</v>
+        <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1771,8 +1776,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1805,66 +1815,66 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Fläckvingad träfluga</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/S 2180-2023 artfynd.xlsx", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/S 2180-2023 karta.png", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/S 2180-2023 georefererad karta.tif", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/S 2180-2023 FSC-klagomål.docx", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/S 2180-2023 FSC-klagomål mail.docx", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/S 2180-2023 tillsynsbegäran.docx", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/S 2180-2023 tillsynsbegäran mail.docx", "S 2180-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>S 2180-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45222</v>
+        <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1877,7 +1887,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1886,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1901,26 +1911,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fläckvingad träfluga</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/S 2180-2023 artfynd.xlsx", "S 2180-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/S 2180-2023 karta.png", "S 2180-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/S 2180-2023 georefererad karta.tif", "S 2180-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/S 2180-2023 FSC-klagomål.docx", "S 2180-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/S 2180-2023 FSC-klagomål mail.docx", "S 2180-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/S 2180-2023 tillsynsbegäran.docx", "S 2180-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/S 2180-2023 tillsynsbegäran mail.docx", "S 2180-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1930,14 +1972,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1950,7 +1992,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1993,7 +2035,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2003,14 +2045,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2023,7 +2065,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2066,7 +2108,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2083,7 +2125,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2096,7 +2138,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2139,7 +2181,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2156,7 +2198,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2211,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2254,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2229,7 +2271,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2284,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2285,7 +2327,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2302,7 +2344,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2357,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2400,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2375,7 +2417,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2430,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>9.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2473,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2448,7 +2490,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2503,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2546,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2521,7 +2563,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2534,7 +2576,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2594,7 +2636,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2667,7 +2709,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2723,7 +2765,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2740,7 +2782,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2795,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2838,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2813,7 +2855,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2868,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2911,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2886,7 +2928,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2899,7 +2941,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2942,7 +2984,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2959,7 +3001,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2972,7 +3014,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3015,7 +3057,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3032,7 +3074,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3045,7 +3087,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3088,7 +3130,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3105,7 +3147,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3118,7 +3160,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3161,7 +3203,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3178,7 +3220,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3191,7 +3233,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3251,7 +3293,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3324,7 +3366,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3397,7 +3439,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3453,7 +3495,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3470,7 +3512,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3483,7 +3525,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3526,7 +3568,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3540,10 +3582,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3556,7 +3598,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3599,7 +3641,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3609,14 +3651,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3629,7 +3671,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3672,7 +3714,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3682,14 +3724,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45826</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3702,7 +3744,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3745,7 +3787,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3755,14 +3797,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3775,7 +3817,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3818,7 +3860,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3832,10 +3874,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44935</v>
+        <v>44915</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3895,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3938,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3906,14 +3948,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3925,13 +3967,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +4011,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3984,14 +4021,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44930</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4003,13 +4040,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4052,7 +4084,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4066,10 +4098,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45251</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4081,8 +4113,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4125,7 +4162,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4139,10 +4176,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4160,7 +4197,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4220,7 +4257,7 @@
         <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4281,7 +4318,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4295,10 +4332,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45359</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4316,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4376,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1979,7 +1979,7 @@
         <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,7 +2052,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2125,7 +2125,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2198,7 +2198,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2271,7 +2271,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2344,7 +2344,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2400,7 +2400,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2417,7 +2417,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9.4</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2490,7 +2490,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2563,7 +2563,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,7 +2636,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2709,7 +2709,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2782,7 +2782,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2855,7 +2855,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2928,7 +2928,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3001,7 +3001,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,7 +3074,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3147,7 +3147,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3220,7 +3220,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3293,7 +3293,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3366,7 +3366,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3439,7 +3439,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3512,7 +3512,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45251</v>
+        <v>44935</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3670,8 +3670,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3714,7 +3719,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3731,7 +3736,7 @@
         <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3744,7 +3749,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3787,7 +3792,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3804,7 +3809,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3817,7 +3822,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3860,7 +3865,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3870,14 +3875,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3889,13 +3894,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3967,8 +3967,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4011,7 +4016,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4021,14 +4026,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4041,7 +4046,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4084,7 +4089,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4098,10 +4103,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4119,7 +4124,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4162,7 +4167,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4176,10 +4181,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4197,7 +4202,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4240,7 +4245,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4254,10 +4259,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4275,7 +4280,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4318,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4328,14 +4333,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4347,13 +4352,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,8 +1991,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2035,7 +2040,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,7 +2057,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2065,7 +2070,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2108,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2125,7 +2130,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2138,7 +2143,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2181,7 +2186,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2198,7 +2203,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2211,7 +2216,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2254,7 +2259,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2271,7 +2276,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2284,7 +2289,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2327,7 +2332,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2344,7 +2349,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2357,7 +2362,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2400,7 +2405,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2417,7 +2422,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2430,7 +2435,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2473,7 +2478,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2490,7 +2495,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2503,7 +2508,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2546,7 +2551,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2563,7 +2568,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2576,7 +2581,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2619,7 +2624,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,7 +2641,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2649,7 +2654,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2692,7 +2697,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2709,7 +2714,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2722,7 +2727,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2765,7 +2770,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2782,7 +2787,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2795,7 +2800,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2838,7 +2843,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2855,7 +2860,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2868,7 +2873,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2928,7 +2933,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2984,7 +2989,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3001,7 +3006,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3014,7 +3019,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3057,7 +3062,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,7 +3079,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3087,7 +3092,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3130,7 +3135,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3147,7 +3152,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3160,7 +3165,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3203,7 +3208,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3220,7 +3225,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3233,7 +3238,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3276,7 +3281,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3293,7 +3298,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3306,7 +3311,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3349,7 +3354,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3366,7 +3371,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3379,7 +3384,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3422,7 +3427,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3439,7 +3444,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3452,7 +3457,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3495,7 +3500,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3512,7 +3517,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3525,7 +3530,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3568,7 +3573,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3598,7 +3603,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3641,7 +3646,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3651,14 +3656,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44935</v>
+        <v>45826</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3670,13 +3675,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3733,10 +3733,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>45251</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45995</v>
+        <v>45222</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4030,10 +4030,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45359</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4045,8 +4045,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4089,7 +4094,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4103,10 +4108,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>45078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4124,7 +4129,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4167,7 +4172,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4181,10 +4186,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>44935</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4202,7 +4207,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4245,7 +4250,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4259,10 +4264,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45995</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4274,13 +4279,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>45995</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32951-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,14 +1431,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,11 +1450,16 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1487,162 +1492,157 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 32951-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Etternässla
 Kopparödla</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46919-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45201</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1671,8 +1671,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1681,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1699,55 +1704,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1757,14 +1762,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1776,13 +1781,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1791,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,48 +1809,48 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44915</v>
+        <v>44935</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2050,14 +2050,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2123,14 +2123,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2196,14 +2196,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2215,8 +2215,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2259,7 +2264,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2269,14 +2274,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2289,7 +2294,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2332,7 +2337,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2342,14 +2347,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2361,8 +2366,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2405,7 +2415,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2415,14 +2425,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2434,8 +2444,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2478,7 +2493,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2495,7 +2510,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2508,7 +2523,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9.4</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2551,7 +2566,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2561,14 +2576,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2580,8 +2595,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2624,7 +2644,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2638,10 +2658,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2654,7 +2674,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2697,7 +2717,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2714,7 +2734,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2727,7 +2747,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2770,7 +2790,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2787,7 +2807,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2800,7 +2820,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2843,7 +2863,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2860,7 +2880,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2873,7 +2893,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2916,7 +2936,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2933,7 +2953,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2946,7 +2966,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2989,7 +3009,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3006,7 +3026,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3019,7 +3039,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3062,7 +3082,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3079,7 +3099,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3092,7 +3112,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3135,7 +3155,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3152,7 +3172,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3165,7 +3185,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3208,7 +3228,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3225,7 +3245,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3238,7 +3258,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3281,7 +3301,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3298,7 +3318,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3311,7 +3331,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>10.5</v>
+        <v>1.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3354,7 +3374,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3371,7 +3391,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3384,7 +3404,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3427,7 +3447,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3444,7 +3464,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3457,7 +3477,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3500,7 +3520,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3517,7 +3537,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3530,7 +3550,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3590,7 +3610,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3646,7 +3666,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3660,10 +3680,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3696,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3719,7 +3739,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3729,14 +3749,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3769,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3792,7 +3812,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3806,10 +3826,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3822,7 +3842,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3865,7 +3885,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3882,7 +3902,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3895,7 +3915,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3938,7 +3958,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3948,14 +3968,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3967,13 +3987,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4016,7 +4031,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4026,14 +4041,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4045,13 +4060,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4094,7 +4104,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4104,14 +4114,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4123,13 +4133,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4172,7 +4177,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4182,14 +4187,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,13 +4206,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45995</v>
+        <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44935</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44915</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>44935</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45995</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44930</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45251</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>44915</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>45359</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4194,7 +4194,7 @@
         <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>45839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44935</v>
+        <v>45251</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,13 +1991,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2040,7 +2035,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2050,14 +2045,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2070,7 +2065,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2113,7 +2108,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45995</v>
+        <v>44915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,8 +2137,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2215,13 +2215,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2264,7 +2259,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2278,10 +2273,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45251</v>
+        <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2294,7 +2289,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2337,7 +2332,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2347,14 +2342,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44915</v>
+        <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2366,13 +2361,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2415,7 +2405,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2429,10 +2419,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45078</v>
+        <v>44930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2450,7 +2440,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2493,7 +2483,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2503,14 +2493,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2520,6 +2510,11 @@
       <c r="G21" t="inlineStr">
         <is>
           <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -2566,7 +2561,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2601,7 +2596,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2644,7 +2639,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2654,14 +2649,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45222</v>
+        <v>44935</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2673,8 +2668,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2734,7 +2734,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2807,7 +2807,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2880,7 +2880,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2953,7 +2953,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3009,7 +3009,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3026,7 +3026,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3099,7 +3099,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3155,7 +3155,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3172,7 +3172,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3228,7 +3228,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3245,7 +3245,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3301,7 +3301,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3318,7 +3318,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3391,7 +3391,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3464,7 +3464,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3520,7 +3520,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3537,7 +3537,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10.5</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3593,7 +3593,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3610,7 +3610,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3666,7 +3666,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3683,7 +3683,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3756,7 +3756,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3812,7 +3812,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3829,7 +3829,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3902,7 +3902,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3975,7 +3975,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4031,7 +4031,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4048,7 +4048,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4104,7 +4104,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4121,7 +4121,7 @@
         <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4177,7 +4177,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4194,7 +4194,7 @@
         <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4267,7 +4267,7 @@
         <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32951-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,14 +1431,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,16 +1450,11 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1492,157 +1487,162 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Etternässla
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46919-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45201</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Tofsmes</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32951-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Etternässla
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1671,13 +1671,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1686,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1704,55 +1699,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1762,14 +1757,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1781,8 +1776,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1791,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,48 +1809,48 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45251</v>
+        <v>44935</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,8 +1991,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2035,7 +2040,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2052,7 +2057,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2065,7 +2070,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2108,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2118,14 +2123,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,13 +2142,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2196,14 +2196,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2259,7 +2259,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2269,14 +2269,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2415,14 +2415,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2434,13 +2434,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2483,7 +2478,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2493,14 +2488,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2512,13 +2507,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2561,7 +2551,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2571,14 +2561,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2590,13 +2580,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2639,7 +2624,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2649,14 +2634,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2668,13 +2653,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2717,7 +2697,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2734,7 +2714,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2747,7 +2727,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2790,7 +2770,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2807,7 +2787,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2820,7 +2800,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2863,7 +2843,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2880,7 +2860,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2893,7 +2873,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>10.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2936,7 +2916,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2953,7 +2933,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2966,7 +2946,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3009,7 +2989,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3026,7 +3006,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3039,7 +3019,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3082,7 +3062,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3099,7 +3079,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3112,7 +3092,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3155,7 +3135,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3172,7 +3152,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3185,7 +3165,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.4</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3228,7 +3208,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3245,7 +3225,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3258,7 +3238,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3301,7 +3281,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3318,7 +3298,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3331,7 +3311,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3374,7 +3354,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3391,7 +3371,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3404,7 +3384,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3447,7 +3427,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3464,7 +3444,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3477,7 +3457,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3520,7 +3500,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3537,7 +3517,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3550,7 +3530,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3593,7 +3573,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3610,7 +3590,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3623,7 +3603,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3666,7 +3646,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3680,10 +3660,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3696,7 +3676,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3739,7 +3719,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3756,7 +3736,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3769,7 +3749,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3812,7 +3792,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3822,14 +3802,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3842,7 +3822,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3885,7 +3865,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3895,14 +3875,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3915,7 +3895,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3958,7 +3938,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3968,14 +3948,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3987,8 +3967,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4031,7 +4016,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4041,14 +4026,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4061,7 +4046,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4104,7 +4089,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4114,14 +4099,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4133,8 +4118,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4177,7 +4167,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4187,14 +4177,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4206,8 +4196,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4250,7 +4245,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4260,14 +4255,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4279,8 +4274,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45826</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,13 +1991,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2040,7 +2035,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,7 +2052,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2070,7 +2065,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2113,7 +2108,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2130,7 +2125,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2143,7 +2138,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2203,7 +2198,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,7 +2271,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2349,7 +2344,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2405,7 +2400,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2422,7 +2417,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2435,7 +2430,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2478,7 +2473,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2495,7 +2490,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2508,7 +2503,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2551,7 +2546,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2568,7 +2563,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2576,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2624,7 +2619,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2641,7 +2636,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2654,7 +2649,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2697,7 +2692,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2714,7 +2709,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2727,7 +2722,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2770,7 +2765,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2787,7 +2782,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2800,7 +2795,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2843,7 +2838,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2860,7 +2855,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2873,7 +2868,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2916,7 +2911,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2933,7 +2928,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2946,7 +2941,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2989,7 +2984,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3006,7 +3001,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3019,7 +3014,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3062,7 +3057,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3079,7 +3074,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3092,7 +3087,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3135,7 +3130,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3152,7 +3147,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3165,7 +3160,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3208,7 +3203,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3225,7 +3220,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3238,7 +3233,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>10.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3281,7 +3276,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3298,7 +3293,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3311,7 +3306,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3354,7 +3349,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3371,7 +3366,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3384,7 +3379,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3427,7 +3422,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3444,7 +3439,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,7 +3495,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3517,7 +3512,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3530,7 +3525,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3573,7 +3568,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3603,7 +3598,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3646,7 +3641,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3656,14 +3651,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45826</v>
+        <v>45251</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3671,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3719,7 +3714,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3729,14 +3724,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3744,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3809,7 +3804,7 @@
         <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3865,7 +3860,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3879,10 +3874,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45995</v>
+        <v>44915</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3894,8 +3889,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3948,14 +3948,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3967,13 +3967,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4016,7 +4011,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4026,14 +4021,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45251</v>
+        <v>45222</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4046,7 +4041,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4089,7 +4084,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4103,10 +4098,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44915</v>
+        <v>44930</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4124,7 +4119,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4167,7 +4162,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4181,10 +4176,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45078</v>
+        <v>45359</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4202,7 +4197,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4245,7 +4240,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4259,10 +4254,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45359</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4275,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4323,7 +4318,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4333,14 +4328,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45222</v>
+        <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4352,8 +4347,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2990-2023</t>
+          <t>A 2992-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1265,163 +1265,163 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Rynkskinn
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2992-2023 artfynd.xlsx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2992-2023 karta.png", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2992-2023 georefererad karta.tif", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2992-2023 FSC-klagomål.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2992-2023 FSC-klagomål mail.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2992-2023 tillsynsbegäran.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2992-2023 tillsynsbegäran mail.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 2990-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Granbarkgnagare
 Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2990-2023 artfynd.xlsx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2990-2023 karta.png", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2990-2023 georefererad karta.tif", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2990-2023 FSC-klagomål.docx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2990-2023 FSC-klagomål mail.docx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2990-2023 tillsynsbegäran.docx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2990-2023 tillsynsbegäran mail.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 2992-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Kandelabersvamp
-Rynkskinn
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2992-2023 artfynd.xlsx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2992-2023 karta.png", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2992-2023 georefererad karta.tif", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2992-2023 FSC-klagomål.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2992-2023 FSC-klagomål mail.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2992-2023 tillsynsbegäran.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2992-2023 tillsynsbegäran mail.docx", "A 2992-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32951-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,14 +1431,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,11 +1450,16 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1487,155 +1492,150 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 32951-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Etternässla
 Kopparödla</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46919-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45201</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
         <v/>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,8 +1991,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2035,7 +2040,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2045,14 +2050,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45839</v>
+        <v>45251</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2065,7 +2070,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2108,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2118,14 +2123,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2137,8 +2142,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2181,7 +2191,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2198,7 +2208,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2211,7 +2221,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2254,7 +2264,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2271,7 +2281,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2284,7 +2294,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2327,7 +2337,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2344,7 +2354,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2357,7 +2367,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2400,7 +2410,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2417,7 +2427,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2430,7 +2440,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9.4</v>
+        <v>2.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2473,7 +2483,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2490,7 +2500,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2503,7 +2513,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2546,7 +2556,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2563,7 +2573,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2576,7 +2586,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2619,7 +2629,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2636,7 +2646,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2649,7 +2659,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2692,7 +2702,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2709,7 +2719,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2722,7 +2732,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2765,7 +2775,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2782,7 +2792,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2795,7 +2805,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2838,7 +2848,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2855,7 +2865,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2868,7 +2878,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2911,7 +2921,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2928,7 +2938,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2941,7 +2951,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2984,7 +2994,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3001,7 +3011,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3014,7 +3024,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3057,7 +3067,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3074,7 +3084,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3087,7 +3097,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3130,7 +3140,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3147,7 +3157,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3160,7 +3170,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3203,7 +3213,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3220,7 +3230,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3233,7 +3243,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.5</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3276,7 +3286,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3293,7 +3303,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3306,7 +3316,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3349,7 +3359,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3366,7 +3376,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3379,7 +3389,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3422,7 +3432,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3439,7 +3449,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3452,7 +3462,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3495,7 +3505,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3512,7 +3522,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3525,7 +3535,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3568,7 +3578,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3582,10 +3592,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3598,7 +3608,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3641,7 +3651,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3651,14 +3661,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3671,7 +3681,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3714,7 +3724,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3724,14 +3734,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3744,7 +3754,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>9.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3787,7 +3797,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3797,14 +3807,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45995</v>
+        <v>45826</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3817,7 +3827,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3860,7 +3870,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3874,10 +3884,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44915</v>
+        <v>45078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3895,7 +3905,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3955,7 +3965,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4011,7 +4021,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4021,14 +4031,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45222</v>
+        <v>45359</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4040,8 +4050,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4084,7 +4099,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4098,10 +4113,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44930</v>
+        <v>45995</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4113,13 +4128,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4162,7 +4172,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4176,10 +4186,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45359</v>
+        <v>45995</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4191,13 +4201,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4240,7 +4245,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4250,14 +4255,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4269,13 +4274,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4335,7 +4335,7 @@
         <v>44935</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2992-2023</t>
+          <t>A 2990-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1265,163 +1265,163 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare
+Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2990-2023 artfynd.xlsx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2990-2023 karta.png", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2990-2023 georefererad karta.tif", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2990-2023 FSC-klagomål.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2990-2023 FSC-klagomål mail.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2990-2023 tillsynsbegäran.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2990-2023 tillsynsbegäran mail.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 2992-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Rynkskinn
 Blåmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2992-2023 artfynd.xlsx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2992-2023 karta.png", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2992-2023 georefererad karta.tif", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2992-2023 FSC-klagomål.docx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2992-2023 FSC-klagomål mail.docx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2992-2023 tillsynsbegäran.docx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2992-2023 tillsynsbegäran mail.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 2990-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare
-Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2990-2023 artfynd.xlsx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2990-2023 karta.png", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2990-2023 georefererad karta.tif", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2990-2023 FSC-klagomål.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2990-2023 FSC-klagomål mail.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2990-2023 tillsynsbegäran.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2990-2023 tillsynsbegäran mail.docx", "A 2990-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32951-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,14 +1431,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,16 +1450,11 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1492,150 +1487,155 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Etternässla
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46919-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45201</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Tofsmes</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32951-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Etternässla
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
         <v/>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44930</v>
+        <v>45359</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2040,7 +2040,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45251</v>
+        <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2069,8 +2069,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2113,7 +2118,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2127,10 +2132,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44915</v>
+        <v>44935</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2148,7 +2153,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2191,7 +2196,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2201,14 +2206,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2221,7 +2226,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2264,7 +2269,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2274,14 +2279,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2294,7 +2299,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2337,7 +2342,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2354,7 +2359,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2367,7 +2372,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2410,7 +2415,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2427,7 +2432,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2440,7 +2445,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2483,7 +2488,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2500,7 +2505,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2513,7 +2518,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2556,7 +2561,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2573,7 +2578,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2586,7 +2591,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2629,7 +2634,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2646,7 +2651,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2659,7 +2664,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2702,7 +2707,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2719,7 +2724,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2732,7 +2737,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2775,7 +2780,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2792,7 +2797,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2805,7 +2810,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>9.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2848,7 +2853,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2865,7 +2870,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2878,7 +2883,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2921,7 +2926,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2938,7 +2943,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2951,7 +2956,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2994,7 +2999,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3011,7 +3016,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3024,7 +3029,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3067,7 +3072,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3084,7 +3089,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3097,7 +3102,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3140,7 +3145,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3157,7 +3162,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3170,7 +3175,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3213,7 +3218,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3230,7 +3235,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3243,7 +3248,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3286,7 +3291,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3303,7 +3308,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3316,7 +3321,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3359,7 +3364,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3376,7 +3381,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3389,7 +3394,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3432,7 +3437,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3449,7 +3454,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3462,7 +3467,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3505,7 +3510,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3522,7 +3527,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3535,7 +3540,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3578,7 +3583,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3595,7 +3600,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3608,7 +3613,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>10.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3651,7 +3656,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3668,7 +3673,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3681,7 +3686,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3724,7 +3729,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3741,7 +3746,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3754,7 +3759,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3797,7 +3802,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3811,10 +3816,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3827,7 +3832,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3870,7 +3875,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3880,14 +3885,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3899,13 +3904,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3948,7 +3948,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45359</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4048,11 +4048,6 @@
       <c r="G42" t="inlineStr">
         <is>
           <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -4099,7 +4094,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4113,10 +4108,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45995</v>
+        <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4129,7 +4124,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4172,7 +4167,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4186,10 +4181,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45995</v>
+        <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,8 +4196,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44935</v>
+        <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45359</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44935</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45359</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45078</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
         <v>44935</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>45826</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4262,7 +4262,7 @@
         <v>45222</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         <v>44930</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>45201</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45359</v>
+        <v>45222</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,13 +1991,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2040,7 +2035,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,10 +2049,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45078</v>
+        <v>44935</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,7 +2070,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2118,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2132,10 +2127,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44935</v>
+        <v>45995</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2147,13 +2142,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2213,7 +2203,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2269,7 +2259,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2279,14 +2269,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2342,7 +2332,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2359,7 +2349,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2372,7 +2362,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2415,7 +2405,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2432,7 +2422,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2445,7 +2435,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2488,7 +2478,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2505,7 +2495,7 @@
         <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2518,7 +2508,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2561,7 +2551,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2578,7 +2568,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2591,7 +2581,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2634,7 +2624,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2651,7 +2641,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2664,7 +2654,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2707,7 +2697,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2724,7 +2714,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2737,7 +2727,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2780,7 +2770,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2797,7 +2787,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2810,7 +2800,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2853,7 +2843,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2870,7 +2860,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2883,7 +2873,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2926,7 +2916,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2943,7 +2933,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2956,7 +2946,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2999,7 +2989,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3016,7 +3006,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3029,7 +3019,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3072,7 +3062,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3089,7 +3079,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3102,7 +3092,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3145,7 +3135,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3162,7 +3152,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3175,7 +3165,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3235,7 +3225,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3291,7 +3281,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3308,7 +3298,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3321,7 +3311,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3364,7 +3354,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3381,7 +3371,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3394,7 +3384,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3437,7 +3427,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3454,7 +3444,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3467,7 +3457,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3510,7 +3500,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3527,7 +3517,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3540,7 +3530,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3583,7 +3573,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3600,7 +3590,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3613,7 +3603,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3656,7 +3646,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3673,7 +3663,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3686,7 +3676,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3729,7 +3719,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3746,7 +3736,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3759,7 +3749,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3802,7 +3792,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3819,7 +3809,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3832,7 +3822,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3875,7 +3865,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3889,10 +3879,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3905,7 +3895,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3948,7 +3938,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3962,10 +3952,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3978,7 +3968,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4021,7 +4011,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4031,14 +4021,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4050,8 +4040,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4111,7 +4106,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4184,7 +4179,7 @@
         <v>44915</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4245,7 +4240,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4255,14 +4250,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45222</v>
+        <v>45078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4274,8 +4269,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44930</v>
+        <v>45359</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44945</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 32951-2025</t>
+          <t>A 46919-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,14 +1431,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45839</v>
+        <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,11 +1450,16 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1487,162 +1492,157 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 32951-2025</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Etternässla
 Kopparödla</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 46919-2023</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45201</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1671,8 +1671,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1681,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1699,55 +1704,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1757,14 +1762,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1776,13 +1781,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1791,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,48 +1809,48 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1972,14 +1972,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45222</v>
+        <v>45251</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>44935</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45995</v>
+        <v>44915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,8 +2142,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2203,7 +2208,7 @@
         <v>45995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2259,7 +2264,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2269,14 +2274,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2332,7 +2337,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2346,10 +2351,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2362,7 +2367,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2405,7 +2410,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2415,14 +2420,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45839</v>
+        <v>44930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2434,8 +2439,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2478,7 +2488,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2488,14 +2498,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2507,8 +2517,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2551,7 +2566,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2568,7 +2583,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2596,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2624,7 +2639,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2634,14 +2649,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2653,8 +2668,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2697,7 +2717,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2714,7 +2734,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2727,7 +2747,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2770,7 +2790,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2787,7 +2807,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2800,7 +2820,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2843,7 +2863,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2860,7 +2880,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2873,7 +2893,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2916,7 +2936,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2933,7 +2953,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2946,7 +2966,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2989,7 +3009,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3006,7 +3026,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3019,7 +3039,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3062,7 +3082,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3079,7 +3099,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3092,7 +3112,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10.5</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3135,7 +3155,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3152,7 +3172,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3165,7 +3185,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3208,7 +3228,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3225,7 +3245,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3238,7 +3258,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3281,7 +3301,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3298,7 +3318,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3311,7 +3331,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3354,7 +3374,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3371,7 +3391,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3384,7 +3404,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.2</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3427,7 +3447,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3444,7 +3464,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3457,7 +3477,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3500,7 +3520,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3517,7 +3537,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3530,7 +3550,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3573,7 +3593,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3590,7 +3610,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3603,7 +3623,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3646,7 +3666,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3663,7 +3683,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3696,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3719,7 +3739,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3736,7 +3756,7 @@
         <v>45839</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3769,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3792,7 +3812,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3809,7 +3829,7 @@
         <v>45839</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3822,7 +3842,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9.4</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3865,7 +3885,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3879,10 +3899,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3895,7 +3915,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3938,7 +3958,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3955,7 +3975,7 @@
         <v>45839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3968,7 +3988,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.6</v>
+        <v>10.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4011,7 +4031,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4021,14 +4041,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4040,13 +4060,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4089,7 +4104,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4099,14 +4114,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4162,7 +4177,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4172,14 +4187,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4191,13 +4206,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4240,7 +4250,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4250,14 +4260,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4269,13 +4279,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4318,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4328,14 +4333,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45359</v>
+        <v>45826</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4347,13 +4352,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2990-2023</t>
+          <t>A 2992-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1265,156 +1265,156 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp
+Rynkskinn
+Blåmossa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2992-2023 artfynd.xlsx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2992-2023 karta.png", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2992-2023 georefererad karta.tif", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2992-2023 FSC-klagomål.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2992-2023 FSC-klagomål mail.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2992-2023 tillsynsbegäran.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2992-2023 tillsynsbegäran mail.docx", "A 2992-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 2990-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>4</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Granbarkgnagare
 Större vattensalamander
 Mindre vattensalamander</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2990-2023 artfynd.xlsx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2990-2023 karta.png", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2990-2023 georefererad karta.tif", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2990-2023 FSC-klagomål.docx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2990-2023 FSC-klagomål mail.docx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2990-2023 tillsynsbegäran.docx", "A 2990-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2990-2023 tillsynsbegäran mail.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 2992-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Kandelabersvamp
-Rynkskinn
-Blåmossa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2992-2023 artfynd.xlsx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2992-2023 karta.png", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2992-2023 georefererad karta.tif", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2992-2023 FSC-klagomål.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2992-2023 FSC-klagomål mail.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2992-2023 tillsynsbegäran.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2992-2023 tillsynsbegäran mail.docx", "A 2992-2023")</f>
         <v/>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
         <v>45201</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45839</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 2987-2023</t>
+          <t>A 33473-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44945</v>
+        <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1671,13 +1671,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1686,10 +1681,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1704,55 +1699,55 @@
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 33473-2025</t>
+          <t>A 2987-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1762,14 +1757,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45839</v>
+        <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1781,8 +1776,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1791,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,48 +1809,48 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 33473-2025 artfynd.xlsx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2987-2023 artfynd.xlsx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 33473-2025 karta.png", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2987-2023 karta.png", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 33473-2025 georefererad karta.tif", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2987-2023 georefererad karta.tif", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 33473-2025 FSC-klagomål.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2987-2023 FSC-klagomål.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 33473-2025 FSC-klagomål mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2987-2023 FSC-klagomål mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 33473-2025 tillsynsbegäran.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2987-2023 tillsynsbegäran.docx", "A 2987-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 33473-2025 tillsynsbegäran mail.docx", "A 33473-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2987-2023 tillsynsbegäran mail.docx", "A 2987-2023")</f>
         <v/>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45251</v>
+        <v>44930</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1991,8 +1991,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2035,7 +2040,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 32962-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2045,14 +2050,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44935</v>
+        <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2064,13 +2069,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 33029-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2123,14 +2123,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44915</v>
+        <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2142,13 +2142,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2191,7 +2186,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 33455-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2201,14 +2196,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2221,7 +2216,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2264,7 +2259,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 33243-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2274,14 +2269,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45995</v>
+        <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2294,7 +2289,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2337,7 +2332,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 33251-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2351,10 +2346,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45222</v>
+        <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2367,7 +2362,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2410,7 +2405,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 33277-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2420,14 +2415,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44930</v>
+        <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2439,13 +2434,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2488,7 +2478,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2502,10 +2492,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45359</v>
+        <v>45251</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2517,13 +2507,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2566,7 +2551,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2583,7 +2568,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2596,7 +2581,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2639,7 +2624,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2649,14 +2634,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2668,13 +2653,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2717,7 +2697,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2734,7 +2714,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2747,7 +2727,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2790,7 +2770,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2807,7 +2787,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2820,7 +2800,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2863,7 +2843,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 33277-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2880,7 +2860,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2893,7 +2873,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2936,7 +2916,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 33455-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2953,7 +2933,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2966,7 +2946,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>10.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3009,7 +2989,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 33243-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3026,7 +3006,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3039,7 +3019,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3082,7 +3062,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33251-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3099,7 +3079,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3112,7 +3092,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3155,7 +3135,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3172,7 +3152,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3185,7 +3165,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>9.4</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3228,7 +3208,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3245,7 +3225,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3258,7 +3238,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3301,7 +3281,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33029-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3318,7 +3298,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3331,7 +3311,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3374,7 +3354,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3391,7 +3371,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3404,7 +3384,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3447,7 +3427,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3464,7 +3444,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3477,7 +3457,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3520,7 +3500,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3537,7 +3517,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3550,7 +3530,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3593,7 +3573,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3610,7 +3590,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3623,7 +3603,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3666,7 +3646,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3683,7 +3663,7 @@
         <v>45839</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3696,7 +3676,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>9.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3739,7 +3719,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32962-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3753,10 +3733,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3769,7 +3749,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3812,7 +3792,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3822,14 +3802,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45839</v>
+        <v>44915</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3841,8 +3821,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3885,7 +3870,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3895,14 +3880,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45839</v>
+        <v>45078</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3914,8 +3899,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3958,7 +3948,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3968,14 +3958,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3988,7 +3978,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4031,7 +4021,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4041,14 +4031,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45839</v>
+        <v>45995</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4061,7 +4051,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4104,7 +4094,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4114,14 +4104,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45839</v>
+        <v>45359</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4133,8 +4123,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4177,7 +4172,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4191,10 +4186,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4207,7 +4202,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4250,7 +4245,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4260,14 +4255,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45839</v>
+        <v>44935</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4279,8 +4274,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45826</v>
+        <v>45839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt SALEM.xlsx
+++ b/Översikt SALEM.xlsx
@@ -601,7 +601,7 @@
         <v>45359</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
         <v>45534</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45352</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>44915</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>44529</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 2992-2023</t>
+          <t>A 2990-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>44945</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1265,163 +1265,163 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare
+Större vattensalamander
+Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2990-2023 artfynd.xlsx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2990-2023 karta.png", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2990-2023 georefererad karta.tif", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2990-2023 FSC-klagomål.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2990-2023 FSC-klagomål mail.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2990-2023 tillsynsbegäran.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2990-2023 tillsynsbegäran mail.docx", "A 2990-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 2992-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44945</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Kandelabersvamp
 Rynkskinn
 Blåmossa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2992-2023 artfynd.xlsx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2992-2023 karta.png", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2992-2023 georefererad karta.tif", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2992-2023 FSC-klagomål.docx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2992-2023 FSC-klagomål mail.docx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2992-2023 tillsynsbegäran.docx", "A 2992-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2992-2023 tillsynsbegäran mail.docx", "A 2992-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 2990-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44945</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Granbarkgnagare
-Större vattensalamander
-Mindre vattensalamander</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 2990-2023 artfynd.xlsx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 2990-2023 karta.png", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 2990-2023 georefererad karta.tif", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 2990-2023 FSC-klagomål.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 2990-2023 FSC-klagomål mail.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 2990-2023 tillsynsbegäran.docx", "A 2990-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 2990-2023 tillsynsbegäran mail.docx", "A 2990-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 46919-2023</t>
+          <t>A 32951-2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1431,14 +1431,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45201</v>
+        <v>45839</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1450,16 +1450,11 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1492,150 +1487,155 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Etternässla
+Kopparödla</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 46919-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45201</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>STOCKHOLMS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SALEM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Tofsmes</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 46919-2023 artfynd.xlsx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 46919-2023 karta.png", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 46919-2023 georefererad karta.tif", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 46919-2023 FSC-klagomål.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 46919-2023 FSC-klagomål mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 46919-2023 tillsynsbegäran.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 46919-2023 tillsynsbegäran mail.docx", "A 46919-2023")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0128/fåglar/A 46919-2023 prioriterade fågelarter.docx", "A 46919-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 32951-2025</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>STOCKHOLMS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SALEM</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Etternässla
-Kopparödla</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/artfynd/A 32951-2025 artfynd.xlsx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor/A 32951-2025 karta.png", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/kartor_geotiff/A 32951-2025 georefererad karta.tif", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomål/A 32951-2025 FSC-klagomål.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/klagomålsmail/A 32951-2025 FSC-klagomål mail.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsyn/A 32951-2025 tillsynsbegäran.docx", "A 32951-2025")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0128/tillsynsmail/A 32951-2025 tillsynsbegäran mail.docx", "A 32951-2025")</f>
         <v/>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         <v>45839</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>44945</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>45098</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 504-2023</t>
+          <t>A 1071-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44930</v>
+        <v>44935</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         <v>45839</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>45839</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>45839</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>45839</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>45839</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45839</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58592-2023</t>
+          <t>A 33284-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2488,14 +2488,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45251</v>
+        <v>45839</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2551,7 +2551,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 33284-2025</t>
+          <t>A 32960-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2568,7 +2568,7 @@
         <v>45839</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 32960-2025</t>
+          <t>A 32968-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2641,7 +2641,7 @@
         <v>45839</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 32968-2025</t>
+          <t>A 32942-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2714,7 +2714,7 @@
         <v>45839</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 32942-2025</t>
+          <t>A 32965-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2787,7 +2787,7 @@
         <v>45839</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2843,7 +2843,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 32965-2025</t>
+          <t>A 32970-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2860,7 +2860,7 @@
         <v>45839</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>10.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2916,7 +2916,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 32970-2025</t>
+          <t>A 32953-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2933,7 +2933,7 @@
         <v>45839</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 32953-2025</t>
+          <t>A 33470-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3006,7 +3006,7 @@
         <v>45839</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3062,7 +3062,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 33470-2025</t>
+          <t>A 33441-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3079,7 +3079,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3135,7 +3135,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 33441-2025</t>
+          <t>A 33428-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3152,7 +3152,7 @@
         <v>45839</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3208,7 +3208,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 33428-2025</t>
+          <t>A 33439-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3225,7 +3225,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3281,7 +3281,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 33439-2025</t>
+          <t>A 33460-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3298,7 +3298,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3354,7 +3354,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 33460-2025</t>
+          <t>A 33465-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3371,7 +3371,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33465-2025</t>
+          <t>A 32946-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3444,7 +3444,7 @@
         <v>45839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 32946-2025</t>
+          <t>A 33421-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3517,7 +3517,7 @@
         <v>45839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 33421-2025</t>
+          <t>A 33446-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3590,7 +3590,7 @@
         <v>45839</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>9.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33446-2025</t>
+          <t>A 29982-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45839</v>
+        <v>45826</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9.4</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3719,7 +3719,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 29982-2025</t>
+          <t>A 60731-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3729,14 +3729,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45826</v>
+        <v>45995</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61336-2022</t>
+          <t>A 60733-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3806,10 +3806,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44915</v>
+        <v>45995</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3821,13 +3821,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3870,7 +3865,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 23992-2023</t>
+          <t>A 33281-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3880,14 +3875,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45078</v>
+        <v>45839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3899,13 +3894,8 @@
           <t>SALEM</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3948,7 +3938,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 60731-2025</t>
+          <t>A 504-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3962,10 +3952,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45995</v>
+        <v>44930</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3977,8 +3967,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4021,7 +4016,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 60733-2025</t>
+          <t>A 58592-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4035,10 +4030,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45995</v>
+        <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4051,7 +4046,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4094,7 +4089,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9533-2024</t>
+          <t>A 61336-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4108,10 +4103,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45359</v>
+        <v>44915</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4129,7 +4124,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4172,7 +4167,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 51720-2023</t>
+          <t>A 23992-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4182,14 +4177,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45222</v>
+        <v>45078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4201,8 +4196,13 @@
           <t>SALEM</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 1071-2023</t>
+          <t>A 9533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44935</v>
+        <v>45359</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 33281-2025</t>
+          <t>A 51720-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4337,10 +4337,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45839</v>
+        <v>45222</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>45055</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
